--- a/config/xlsx/tokens.xlsx
+++ b/config/xlsx/tokens.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -550,6 +550,26 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>战令积分</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>res://assets/ui/xianxia_v3_layers_v2/layers/cultivation_exp_icon.png</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>战令活动专用积分，不可兑换或消耗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
